--- a/File crisi.xlsx
+++ b/File crisi.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="385">
   <si>
     <t>Giorno</t>
   </si>
@@ -539,555 +539,558 @@
     <t>7-03-2025 0219-0222 2025-11-20 11-12-08</t>
   </si>
   <si>
+    <t>00:01:18</t>
+  </si>
+  <si>
+    <t>00:02:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:00:39 - 03:01:12 </t>
+  </si>
+  <si>
+    <t>7-03-2025 0255-0302 2025-11-20 11-17-52</t>
+  </si>
+  <si>
+    <t>00:06:11</t>
+  </si>
+  <si>
+    <t>00:06:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:30:51 - 03:31:43 </t>
+  </si>
+  <si>
+    <t>7-03-2025 0330-0333 2025-11-20 11-27-58</t>
+  </si>
+  <si>
+    <t>00:00:59</t>
+  </si>
+  <si>
+    <t>00:01:58</t>
+  </si>
+  <si>
+    <t>03:34:05 - 03:34:37</t>
+  </si>
+  <si>
+    <t>7-03-2025 0334-0335 2025-11-20 11-32-39</t>
+  </si>
+  <si>
+    <t>00:00:08</t>
+  </si>
+  <si>
+    <t>00:00:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:02:12 - 04:02:46 </t>
+  </si>
+  <si>
+    <t>7-03-2025 0401-0405 2025-11-20 11-47-51</t>
+  </si>
+  <si>
+    <t>00:01:12</t>
+  </si>
+  <si>
+    <t>00:01:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:30:33 - 04:31:20 </t>
+  </si>
+  <si>
+    <t>7-03-2025 0429-0432 2025-11-20 11-55-07</t>
+  </si>
+  <si>
+    <t>00:01:45</t>
+  </si>
+  <si>
+    <t>05:03:22 - 05:04:00</t>
+  </si>
+  <si>
+    <t>7-03-2025 0502-0504  2025-11-20 12-00-00</t>
+  </si>
+  <si>
+    <t>00:01:05</t>
+  </si>
+  <si>
+    <t>00:01:39</t>
+  </si>
+  <si>
+    <t>05:22:51 - 05:23:30</t>
+  </si>
+  <si>
+    <t>7-03-2025 0521-0525 2025-11-20 12-03-10</t>
+  </si>
+  <si>
+    <t>00:02:42</t>
+  </si>
+  <si>
+    <t>05:41:40 - 05:42:16</t>
+  </si>
+  <si>
+    <t>7-03-2025 0539-0543  2025-11-20 12-08-54</t>
+  </si>
+  <si>
+    <t>00:02:19</t>
+  </si>
+  <si>
+    <t>00:03:00</t>
+  </si>
+  <si>
+    <t>06:24:23 - 06:25:07</t>
+  </si>
+  <si>
+    <t>7-03-2025 0623-0625 2025-11-20 12-14-36</t>
+  </si>
+  <si>
+    <t>00:00:49</t>
+  </si>
+  <si>
+    <t>00:01:36</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:52:46 - 01:53:48 </t>
+  </si>
+  <si>
+    <t>7-03-2025 0150-0154 2025-11-20 12-18-32</t>
+  </si>
+  <si>
+    <t>00:04:30</t>
+  </si>
+  <si>
+    <t>02:36:25 - 02:37:39</t>
+  </si>
+  <si>
+    <t>7-03-2025 0234-0238  2025-11-20 12-34-33</t>
+  </si>
+  <si>
+    <t>00:03:39</t>
+  </si>
+  <si>
+    <t>Non succede nulla dorme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05:37:03 - 05:37:42 </t>
+  </si>
+  <si>
+    <t>7-03-2025 0536-0538  2025-11-20 12-40-14</t>
+  </si>
+  <si>
+    <t>00:01:50</t>
+  </si>
+  <si>
+    <t>05:49:00 - 05:49:40</t>
+  </si>
+  <si>
+    <t>7-03-2025 0548-0550 2025-11-20 12-44-26</t>
+  </si>
+  <si>
+    <t>00:01:14</t>
+  </si>
+  <si>
+    <t>00:01:59</t>
+  </si>
+  <si>
+    <t>12:31:15 - 12:31:52</t>
+  </si>
+  <si>
+    <t>7-03-2025 1229-1232  2025-11-20 12-54-33</t>
+  </si>
+  <si>
+    <t>00:02:39</t>
+  </si>
+  <si>
+    <t>00:03:22</t>
+  </si>
+  <si>
+    <t>14:19:04 - 14:20:10</t>
+  </si>
+  <si>
+    <t>7-03-2025 1418-1421 2025-11-20 15-07-26</t>
+  </si>
+  <si>
+    <t>Da controllare</t>
+  </si>
+  <si>
+    <t>Ho provato a controllare già io</t>
+  </si>
+  <si>
+    <t>17:48:30 - 17:49:06</t>
+  </si>
+  <si>
+    <t>7-03-2025 1747-1751 2025-11-20 15-21-09</t>
+  </si>
+  <si>
+    <t>00:00:46</t>
+  </si>
+  <si>
+    <t>00:01:29</t>
+  </si>
+  <si>
+    <t>18:57:04 - 18:57:38</t>
+  </si>
+  <si>
+    <t>3-4- 5</t>
+  </si>
+  <si>
+    <t>7-03-2025 1856-1858 2025-11-20 15-26-02</t>
+  </si>
+  <si>
     <t>00:01:03</t>
   </si>
   <si>
-    <t>00:02:02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:00:39 - 03:01:12 </t>
-  </si>
-  <si>
-    <t>7-03-2025 0255-0302 2025-11-20 11-17-52</t>
-  </si>
-  <si>
-    <t>00:06:13</t>
-  </si>
-  <si>
-    <t>00:06:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03:30:51 - 03:31:43 </t>
-  </si>
-  <si>
-    <t>7-03-2025 0330-0333 2025-11-20 11-27-58</t>
-  </si>
-  <si>
-    <t>00:01:01</t>
-  </si>
-  <si>
-    <t>00:01:58</t>
-  </si>
-  <si>
-    <t>03:34:05 - 03:34:37</t>
-  </si>
-  <si>
-    <t>7-03-2025 0334-0335 2025-11-20 11-32-39</t>
-  </si>
-  <si>
-    <t>00:00:08</t>
-  </si>
-  <si>
-    <t>00:00:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:02:12 - 04:02:46 </t>
-  </si>
-  <si>
-    <t>7-03-2025 0401-0405 2025-11-20 11-47-51</t>
-  </si>
-  <si>
-    <t>00:01:12</t>
-  </si>
-  <si>
-    <t>00:01:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:30:33 - 04:31:20 </t>
-  </si>
-  <si>
-    <t>7-03-2025 0429-0432 2025-11-20 11-55-07</t>
-  </si>
-  <si>
-    <t>00:01:45</t>
-  </si>
-  <si>
-    <t>05:03:22 - 05:04:00</t>
-  </si>
-  <si>
-    <t>7-03-2025 0502-0504  2025-11-20 12-00-00</t>
-  </si>
-  <si>
-    <t>00:00:56</t>
-  </si>
-  <si>
-    <t>00:01:39</t>
-  </si>
-  <si>
-    <t>05:22:51 - 05:23:30</t>
-  </si>
-  <si>
-    <t>7-03-2025 0521-0525 2025-11-20 12-03-10</t>
-  </si>
-  <si>
-    <t>05:41:40 - 05:42:16</t>
-  </si>
-  <si>
-    <t>7-03-2025 0539-0543  2025-11-20 12-08-54</t>
-  </si>
-  <si>
-    <t>00:02:19</t>
-  </si>
-  <si>
-    <t>00:03:00</t>
-  </si>
-  <si>
-    <t>06:24:23 - 06:25:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7-03-2025 0623-0625 2025-11-20 12-14-36</t>
-  </si>
-  <si>
-    <t>00:00:49</t>
-  </si>
-  <si>
-    <t>00:01:40</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:52:46 - 01:53:48 </t>
-  </si>
-  <si>
-    <t>7-03-2025 0150-0154 2025-11-20 12-18-32</t>
-  </si>
-  <si>
-    <t>00:04:24</t>
-  </si>
-  <si>
-    <t>02:36:25 - 02:37:39</t>
-  </si>
-  <si>
-    <t>7-03-2025 0234-0238  2025-11-20 12-34-33</t>
-  </si>
-  <si>
-    <t>00:03:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:37:03 - 05:37:42 </t>
-  </si>
-  <si>
-    <t>7-03-2025 0536-0538  2025-11-20 12-40-14</t>
-  </si>
-  <si>
-    <t>00:00:59</t>
+    <t>00:01:44</t>
+  </si>
+  <si>
+    <t>08:19:16 - 08:20:16</t>
+  </si>
+  <si>
+    <t>08-03-2025 0820 2025-11-17 17-18-12</t>
+  </si>
+  <si>
+    <t>00:05:06</t>
+  </si>
+  <si>
+    <t>00:05:57</t>
+  </si>
+  <si>
+    <t>09:29:21 - 09:30:02</t>
+  </si>
+  <si>
+    <t>08-03-2025 09302025-11-17 17-27-03</t>
+  </si>
+  <si>
+    <t>11:12:40 - 11:13:45</t>
+  </si>
+  <si>
+    <t>08-03-2025 1110 2025-11-17 17-31-49</t>
+  </si>
+  <si>
+    <t>00:04:53</t>
+  </si>
+  <si>
+    <t>00:05:39</t>
+  </si>
+  <si>
+    <t>15:09:38 - 15:10:31</t>
+  </si>
+  <si>
+    <t>08-03-2025 15-1530 2025-11-17 17-39-31</t>
+  </si>
+  <si>
+    <t>00:00:35</t>
+  </si>
+  <si>
+    <t>00:01:28</t>
+  </si>
+  <si>
+    <t>15:32:25 - 15:33:29</t>
+  </si>
+  <si>
+    <t>3-4 - 5</t>
+  </si>
+  <si>
+    <t>00:23:30</t>
+  </si>
+  <si>
+    <t>00:24:25</t>
+  </si>
+  <si>
+    <t>19:58:00 - 19:59:00</t>
+  </si>
+  <si>
+    <t>08-03-2025 20 2025-11-17 18-11-25</t>
+  </si>
+  <si>
+    <t>00:00:34</t>
+  </si>
+  <si>
+    <t>00:01:34</t>
+  </si>
+  <si>
+    <t>00:36:10 - 00:36:50</t>
+  </si>
+  <si>
+    <t>10-03-2025 0030-0040 2025-11-19 16-19-17</t>
+  </si>
+  <si>
+    <t>00:02:54</t>
+  </si>
+  <si>
+    <t>00:03:36</t>
+  </si>
+  <si>
+    <t>03:45:15 - 03:46:00</t>
+  </si>
+  <si>
+    <t>10-03-2025 0345 2025-11-19 16-30-47</t>
+  </si>
+  <si>
+    <t>00:07:23</t>
+  </si>
+  <si>
+    <t>00:08:20</t>
+  </si>
+  <si>
+    <t>06:59:00 - 06:59:50</t>
+  </si>
+  <si>
+    <t>10-03-2025 0659-0705 2025-11-19 16-47-22</t>
+  </si>
+  <si>
+    <t>00:03:40</t>
+  </si>
+  <si>
+    <t>00:04:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:01:50 - 06:02:50 </t>
+  </si>
+  <si>
+    <t>10-03-2025 06-0605 2025-11-19 16-58-32</t>
+  </si>
+  <si>
+    <t>00:05:15</t>
+  </si>
+  <si>
+    <t>00:06:55</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>00:42:10 - 00:43:20</t>
+  </si>
+  <si>
+    <t>10-03-2025 0040-0045 2025-11-19 17-14-14</t>
+  </si>
+  <si>
+    <t>00:03:14</t>
+  </si>
+  <si>
+    <t>00:04:18</t>
+  </si>
+  <si>
+    <t>08:56:40 - 08:57:30</t>
+  </si>
+  <si>
+    <t>10-03-2025 0900 2025-11-19 17-23-03</t>
+  </si>
+  <si>
+    <t>00:02:35</t>
+  </si>
+  <si>
+    <t>00:03:12</t>
+  </si>
+  <si>
+    <t>09:08:45 - 09:09:15</t>
+  </si>
+  <si>
+    <t>11-03-2025 0903-0910 2025-11-21 11-45-34</t>
+  </si>
+  <si>
+    <t>00:06:17</t>
+  </si>
+  <si>
+    <t>00:06:58</t>
+  </si>
+  <si>
+    <t>10:45:35 - 10:46:18</t>
+  </si>
+  <si>
+    <t>11-03-2025 1042-1047 2025-11-21 12-05-15</t>
+  </si>
+  <si>
+    <t>00:04:04</t>
+  </si>
+  <si>
+    <t>14:14:30 - 14:15:30</t>
+  </si>
+  <si>
+    <t>11-03-2025 1412-1416 2025-11-21 12-11-25</t>
+  </si>
+  <si>
+    <t>00:02:14</t>
+  </si>
+  <si>
+    <t>14:31:26 - 14:32:24</t>
+  </si>
+  <si>
+    <t>11-03-2025 1429-1433 2025-11-21 12-16-33</t>
+  </si>
+  <si>
+    <t>00:01:51</t>
+  </si>
+  <si>
+    <t>15:43:57 15:44:57</t>
+  </si>
+  <si>
+    <t>11-03-2025 1540-1546 2025-11-21 12-21-30</t>
+  </si>
+  <si>
+    <t>00:03:37</t>
+  </si>
+  <si>
+    <t>16:41:25 - 16:42:31</t>
+  </si>
+  <si>
+    <t>11-03-2025 1638-1643 2025-11-21 13-47-14</t>
+  </si>
+  <si>
+    <t>18:30:21 - 18:31:26</t>
+  </si>
+  <si>
+    <t>11-03-2025 1827-1832 2025-11-21 13-53-11</t>
+  </si>
+  <si>
+    <t>00:04:29</t>
+  </si>
+  <si>
+    <t>19:26:14 - 19:27:02</t>
+  </si>
+  <si>
+    <t>11-03-2025 1925-1928 2025-11-21 13-59-26</t>
+  </si>
+  <si>
+    <t>00:01:00</t>
+  </si>
+  <si>
+    <t>21:07:56 - 21:08:43</t>
+  </si>
+  <si>
+    <t>11-03-2025 2105-2109 2025-11-21 14-03-11</t>
+  </si>
+  <si>
+    <t>00:02:59</t>
+  </si>
+  <si>
+    <t>00:03:44</t>
+  </si>
+  <si>
+    <t>21:49:06 - 21:49:50</t>
+  </si>
+  <si>
+    <t>11-03-2025 2147-2150 2025-11-21 14-08-43</t>
+  </si>
+  <si>
+    <t>00:01:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:12:25 - 22:13:15 </t>
+  </si>
+  <si>
+    <t>11-03-2025 2211-2214 2025-11-21 14-16-42</t>
+  </si>
+  <si>
+    <t>00:01:27</t>
+  </si>
+  <si>
+    <t>22:42:16 - 22:43:07</t>
+  </si>
+  <si>
+    <t>11-03-2025 2241-2244 2025-11-21 14-20-50</t>
+  </si>
+  <si>
+    <t>00:01:22</t>
+  </si>
+  <si>
+    <t>00:02:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:36:20 -23:36:50 </t>
+  </si>
+  <si>
+    <t>11-03-2025 2334-2337 2025-11-21 14-24-50</t>
+  </si>
+  <si>
+    <t>00:02:36</t>
+  </si>
+  <si>
+    <t>Non da fare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:24:00 - 16:24:30 </t>
+  </si>
+  <si>
+    <t>11-03-2025 1623-1625 2025-11-21 14-28-50</t>
+  </si>
+  <si>
+    <t>00:00:51</t>
+  </si>
+  <si>
+    <t>00:01:21</t>
+  </si>
+  <si>
+    <t>Non c’è</t>
+  </si>
+  <si>
+    <t>20:31:39 - 20:32:19</t>
+  </si>
+  <si>
+    <t>11-03-2025 2030-2033 2025-11-21 14-31-28</t>
   </si>
   <si>
     <t>00:01:43</t>
   </si>
   <si>
-    <t>05:49:00 - 05:49:40</t>
-  </si>
-  <si>
-    <t>7-03-2025 0548-0550 2025-11-20 12-44-26</t>
-  </si>
-  <si>
-    <t>00:01:14</t>
-  </si>
-  <si>
-    <t>00:01:59</t>
-  </si>
-  <si>
-    <t>12:31:15 - 12:31:52</t>
-  </si>
-  <si>
-    <t>7-03-2025 1229-1232  2025-11-20 12-54-33</t>
-  </si>
-  <si>
-    <t>00:02:39</t>
-  </si>
-  <si>
-    <t>00:03:22</t>
-  </si>
-  <si>
-    <t>14:19:04 - 14:20:10</t>
-  </si>
-  <si>
-    <t>7-03-2025 1418-1421 2025-11-20 15-07-26</t>
-  </si>
-  <si>
-    <t>Da controllare</t>
-  </si>
-  <si>
-    <t>Ho provato a controllare già io</t>
-  </si>
-  <si>
-    <t>17:48:30 - 17:49:06</t>
-  </si>
-  <si>
-    <t>7-03-2025 1747-1751 2025-11-20 15-21-09</t>
-  </si>
-  <si>
-    <t>00:00:46</t>
-  </si>
-  <si>
-    <t>00:01:29</t>
-  </si>
-  <si>
-    <t>18:57:04 - 18:57:38</t>
-  </si>
-  <si>
-    <t>3-4- 5</t>
-  </si>
-  <si>
-    <t>7-03-2025 1856-1858 2025-11-20 15-26-02</t>
-  </si>
-  <si>
-    <t>00:01:05</t>
-  </si>
-  <si>
-    <t>00:01:44</t>
-  </si>
-  <si>
-    <t>08:19:16 - 08:20:16</t>
-  </si>
-  <si>
-    <t>08-03-2025 0820 2025-11-17 17-18-12</t>
-  </si>
-  <si>
-    <t>00:04:55</t>
-  </si>
-  <si>
-    <t>00:05:57</t>
-  </si>
-  <si>
-    <t>09:29:21 - 09:30:02</t>
-  </si>
-  <si>
-    <t>08-03-2025 09302025-11-17 17-27-03</t>
-  </si>
-  <si>
-    <t>00:01:36</t>
-  </si>
-  <si>
-    <t>11:12:40 - 11:13:45</t>
-  </si>
-  <si>
-    <t>08-03-2025 1110 2025-11-17 17-31-49</t>
-  </si>
-  <si>
-    <t>00:04:33</t>
-  </si>
-  <si>
-    <t>00:05:39</t>
-  </si>
-  <si>
-    <t>15:09:38 - 15:10:31</t>
-  </si>
-  <si>
-    <t>08-03-2025 15-1530 2025-11-17 17-39-31</t>
-  </si>
-  <si>
-    <t>00:00:35</t>
-  </si>
-  <si>
-    <t>00:01:28</t>
-  </si>
-  <si>
-    <t>15:32:25 - 15:33:29</t>
-  </si>
-  <si>
-    <t>3-4 - 5</t>
-  </si>
-  <si>
-    <t>00:23:23</t>
-  </si>
-  <si>
-    <t>00:24:27</t>
-  </si>
-  <si>
-    <t>19:58:00 - 19:59:00</t>
-  </si>
-  <si>
-    <t>08-03-2025 20 2025-11-17 18-11-25</t>
-  </si>
-  <si>
-    <t>00:00:34</t>
-  </si>
-  <si>
-    <t>00:01:34</t>
-  </si>
-  <si>
-    <t>00:36:10 - 00:36:50</t>
-  </si>
-  <si>
-    <t>10-03-2025 0030-0040 2025-11-19 16-19-17</t>
-  </si>
-  <si>
-    <t>00:02:54</t>
-  </si>
-  <si>
-    <t>00:03:36</t>
-  </si>
-  <si>
-    <t>03:45:15 - 03:46:00</t>
-  </si>
-  <si>
-    <t>10-03-2025 0345 2025-11-19 16-30-47</t>
-  </si>
-  <si>
-    <t>00:07:23</t>
-  </si>
-  <si>
-    <t>00:08:45</t>
-  </si>
-  <si>
-    <t>06:59:00 - 06:59:50</t>
-  </si>
-  <si>
-    <t>10-03-2025 0659-0705 2025-11-19 16-47-22</t>
-  </si>
-  <si>
-    <t>00:03:47</t>
-  </si>
-  <si>
-    <t>00:04:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:01:50 - 06:02:50 </t>
-  </si>
-  <si>
-    <t>10-03-2025 06-0605 2025-11-19 16-58-32</t>
-  </si>
-  <si>
-    <t>00:05:29</t>
-  </si>
-  <si>
-    <t>00:06:55</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>00:42:10 - 00:43:20</t>
-  </si>
-  <si>
-    <t>10-03-2025 0040-0045 2025-11-19 17-14-14</t>
-  </si>
-  <si>
-    <t>00:03:08</t>
-  </si>
-  <si>
-    <t>00:04:20</t>
-  </si>
-  <si>
-    <t>08:56:40 - 08:57:30</t>
-  </si>
-  <si>
-    <t>10-03-2025 0900 2025-11-19 17-23-03</t>
-  </si>
-  <si>
-    <t>00:02:21</t>
-  </si>
-  <si>
-    <t>00:03:12</t>
-  </si>
-  <si>
-    <t>09:08:45 - 09:09:15</t>
-  </si>
-  <si>
-    <t>11-03-2025 0903-0910 2025-11-21 11-45-34</t>
-  </si>
-  <si>
-    <t>00:06:17</t>
-  </si>
-  <si>
-    <t>00:06:47</t>
-  </si>
-  <si>
-    <t>10:45:35 - 10:46:18</t>
-  </si>
-  <si>
-    <t>11-03-2025 1042-1047 2025-11-21 12-05-15</t>
-  </si>
-  <si>
-    <t>00:04:04</t>
-  </si>
-  <si>
-    <t>14:14:30 - 14:15:30</t>
-  </si>
-  <si>
-    <t>11-03-2025 1412-1416 2025-11-21 12-11-25</t>
-  </si>
-  <si>
-    <t>00:02:14</t>
-  </si>
-  <si>
-    <t>00:03:14</t>
-  </si>
-  <si>
-    <t>14:31:26 - 14:32:24</t>
-  </si>
-  <si>
-    <t>11-03-2025 1429-1433 2025-11-21 12-16-33</t>
-  </si>
-  <si>
-    <t>00:01:51</t>
-  </si>
-  <si>
-    <t>15:43:57 15:44:57</t>
-  </si>
-  <si>
-    <t>11-03-2025 1540-1546 2025-11-21 12-21-30</t>
-  </si>
-  <si>
-    <t>00:03:37</t>
-  </si>
-  <si>
-    <t>00:04:38</t>
-  </si>
-  <si>
-    <t>16:41:25 - 16:42:31</t>
-  </si>
-  <si>
-    <t>11-03-2025 1638-1643 2025-11-21 13-47-14</t>
-  </si>
-  <si>
-    <t>00:04:22</t>
-  </si>
-  <si>
-    <t>18:30:21 - 18:31:26</t>
-  </si>
-  <si>
-    <t>11-03-2025 1827-1832 2025-11-21 13-53-11</t>
-  </si>
-  <si>
-    <t>00:03:10</t>
-  </si>
-  <si>
-    <t>00:04:30</t>
-  </si>
-  <si>
-    <t>19:26:14 - 19:27:02</t>
-  </si>
-  <si>
-    <t>11-03-2025 1925-1928 2025-11-21 13-59-26</t>
-  </si>
-  <si>
-    <t>00:01:00</t>
-  </si>
-  <si>
-    <t>00:01:49</t>
-  </si>
-  <si>
-    <t>21:07:56 - 21:08:43</t>
-  </si>
-  <si>
-    <t>11-03-2025 2105-2109 2025-11-21 14-03-11</t>
-  </si>
-  <si>
-    <t>00:02:59</t>
-  </si>
-  <si>
-    <t>21:49:06 - 21:49:50</t>
-  </si>
-  <si>
-    <t>11-03-2025 2147-2150 2025-11-21 14-08-43</t>
-  </si>
-  <si>
-    <t>00:01:16</t>
+    <t>00:02:12</t>
+  </si>
+  <si>
+    <t>9:56:40 - 09:58:00</t>
+  </si>
+  <si>
+    <t>12-03-2025 0956-0958 2025-11-20 15-36-50</t>
+  </si>
+  <si>
+    <t>00:01:06</t>
+  </si>
+  <si>
+    <t>00:02:48</t>
+  </si>
+  <si>
+    <t>11:24:26 - 11:25:26</t>
+  </si>
+  <si>
+    <t>12-03-2025 1124-1126 2025-11-20 15-42-45</t>
+  </si>
+  <si>
+    <t>00:00:26</t>
+  </si>
+  <si>
+    <t>11:49:15 - 11:49:58</t>
+  </si>
+  <si>
+    <t>12-03-2025 1148-1150 2025-11-20 15-47-07</t>
+  </si>
+  <si>
+    <t>00:01:04</t>
+  </si>
+  <si>
+    <t>16:11:07 - 16:12:05</t>
+  </si>
+  <si>
+    <t>12-03-2025 1610-1613 2025-11-20 15-50-43</t>
+  </si>
+  <si>
+    <t>07:42:19 - 07:43:06</t>
+  </si>
+  <si>
+    <t>12-03-2025 0741-0744 2025-11-20 15-54-43</t>
+  </si>
+  <si>
+    <t>00:01:11</t>
   </si>
   <si>
     <t>00:02:04</t>
   </si>
   <si>
-    <t xml:space="preserve">22:12:25 - 22:13:15 </t>
-  </si>
-  <si>
-    <t>11-03-2025 2211-2214 2025-11-21 14-16-42</t>
-  </si>
-  <si>
-    <t>00:01:19</t>
-  </si>
-  <si>
-    <t>22:42:16 - 22:43:07</t>
-  </si>
-  <si>
-    <t>11-03-2025 2241-2244 2025-11-21 14-20-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:36:20 -23:36:50 </t>
-  </si>
-  <si>
-    <t>11-03-2025 2334-2337 2025-11-21 14-24-50</t>
-  </si>
-  <si>
-    <t>00:02:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:24:00 - 16:24:30 </t>
-  </si>
-  <si>
-    <t>11-03-2025 1623-1625 2025-11-21 14-28-50</t>
-  </si>
-  <si>
-    <t>00:00:51</t>
-  </si>
-  <si>
-    <t>00:01:21</t>
-  </si>
-  <si>
-    <t>20:31:39 - 20:32:19</t>
-  </si>
-  <si>
-    <t>11-03-2025 2030-2033 2025-11-21 14-31-28</t>
-  </si>
-  <si>
-    <t>00:02:12</t>
-  </si>
-  <si>
-    <t>9:56:40 - 09:58:00</t>
-  </si>
-  <si>
-    <t>12-03-2025 0956-0958 2025-11-20 15-36-50</t>
-  </si>
-  <si>
-    <t>00:02:48</t>
-  </si>
-  <si>
-    <t>11:24:26 - 11:25:26</t>
-  </si>
-  <si>
-    <t>12-03-2025 1124-1126 2025-11-20 15-42-45</t>
-  </si>
-  <si>
-    <t>00:00:26</t>
-  </si>
-  <si>
-    <t>11:49:15 - 11:49:58</t>
-  </si>
-  <si>
-    <t>12-03-2025 1148-1150 2025-11-20 15-47-07</t>
-  </si>
-  <si>
-    <t>00:01:04</t>
-  </si>
-  <si>
-    <t>16:11:07 - 16:12:05</t>
-  </si>
-  <si>
-    <t>12-03-2025 1610-1613  2025-11-20 15-50-43</t>
-  </si>
-  <si>
-    <t>07:42:19 - 07:43:06</t>
-  </si>
-  <si>
-    <t>12-03-2025 0741-0744 2025-11-20 15-54-43</t>
-  </si>
-  <si>
-    <t>00:01:11</t>
-  </si>
-  <si>
     <t>11:33:52 - 11:34:40</t>
   </si>
   <si>
     <t>12-03-2025 1132-1136 2025-11-20 15-59-35</t>
   </si>
   <si>
-    <t>00:02:56</t>
-  </si>
-  <si>
     <t xml:space="preserve">12:43:29 - 12:44:10 </t>
   </si>
   <si>
@@ -1118,13 +1121,13 @@
     <t>14-03-2025 1648-1650 2025-11-20 16-42-22</t>
   </si>
   <si>
-    <t>00:00:39</t>
+    <t>00:00:43</t>
   </si>
   <si>
     <t>23:34:50 - 23:35:20</t>
   </si>
   <si>
-    <t>14-03-2025 2333-2335  2025-11-20 16-46-27</t>
+    <t>14-03-2025 2333-2335 2025-11-20 16-46-27</t>
   </si>
   <si>
     <t>00:02:29</t>
@@ -1136,37 +1139,40 @@
     <t>14-03-2025 2009-2013 2025-11-20 16-53-06</t>
   </si>
   <si>
+    <t>00:02:51</t>
+  </si>
+  <si>
     <t>00:03:46</t>
   </si>
   <si>
     <t xml:space="preserve">20:37:50 - 20:38:40 </t>
   </si>
   <si>
-    <t>14-03-2025 2037-2039  2025-11-20 16-58-53</t>
+    <t>14-03-2025 2037-2039 2025-11-20 16-58-53</t>
+  </si>
+  <si>
+    <t>00:01:17</t>
   </si>
   <si>
     <t>22:33:00 - 22:33:50</t>
   </si>
   <si>
-    <t>14-03-2025 2231-2234  2025-11-20 17-02-15</t>
+    <t>14-03-2025 2231-2234 2025-11-20 17-02-15</t>
   </si>
   <si>
     <t>22:34:10 - 22:34:30</t>
   </si>
   <si>
-    <t>14-03-2025 2233-2235  2025-11-20 17-06-34</t>
-  </si>
-  <si>
-    <t>00:01:27</t>
+    <t>14-03-2025 2233-2235 2025-11-20 17-06-34</t>
   </si>
   <si>
     <t>23:23:40 - 23:24:40</t>
   </si>
   <si>
-    <t>14-03-2025 2322-2325  2025-11-20 17-09-58</t>
-  </si>
-  <si>
-    <t>00:02:03</t>
+    <t>14-03-2025 2322-2325 2025-11-20 17-09-58</t>
+  </si>
+  <si>
+    <t>00:02:05</t>
   </si>
 </sst>
 </file>
@@ -3789,7 +3795,7 @@
         <v>182</v>
       </c>
       <c r="H50" t="s" s="3">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -3801,7 +3807,7 @@
         <v>83</v>
       </c>
       <c r="C51" t="s" s="3">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D51" s="9">
         <v>4</v>
@@ -3810,13 +3816,13 @@
         <v>10</v>
       </c>
       <c r="F51" t="s" s="3">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G51" t="s" s="3">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H51" t="s" s="3">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -3828,7 +3834,7 @@
         <v>83</v>
       </c>
       <c r="C52" t="s" s="3">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D52" s="7">
         <v>45781</v>
@@ -3837,13 +3843,13 @@
         <v>10</v>
       </c>
       <c r="F52" t="s" s="3">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G52" t="s" s="3">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H52" t="s" s="3">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -3852,10 +3858,10 @@
     <row r="53" ht="13.65" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C53" t="s" s="3">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D53" s="7">
         <v>45781</v>
@@ -3864,13 +3870,13 @@
         <v>10</v>
       </c>
       <c r="F53" t="s" s="3">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G53" t="s" s="3">
         <v>82</v>
       </c>
       <c r="H53" t="s" s="3">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -3879,10 +3885,10 @@
     <row r="54" ht="13.65" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C54" t="s" s="3">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D54" s="7">
         <v>45781</v>
@@ -3891,25 +3897,27 @@
         <v>10</v>
       </c>
       <c r="F54" t="s" s="3">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G54" t="s" s="3">
         <v>70</v>
       </c>
       <c r="H54" t="s" s="3">
-        <v>214</v>
-      </c>
-      <c r="I54" s="4"/>
+        <v>215</v>
+      </c>
+      <c r="I54" t="s" s="3">
+        <v>216</v>
+      </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
     </row>
     <row r="55" ht="13.65" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C55" t="s" s="3">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D55" s="7">
         <v>45813</v>
@@ -3918,13 +3926,13 @@
         <v>10</v>
       </c>
       <c r="F55" t="s" s="3">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G55" t="s" s="3">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="H55" t="s" s="3">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -3933,10 +3941,10 @@
     <row r="56" ht="13.65" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C56" t="s" s="3">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D56" s="7">
         <v>45781</v>
@@ -3945,13 +3953,13 @@
         <v>10</v>
       </c>
       <c r="F56" t="s" s="3">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G56" t="s" s="3">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H56" t="s" s="3">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
@@ -3960,10 +3968,10 @@
     <row r="57" ht="13.65" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C57" t="s" s="3">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D57" s="7">
         <v>45781</v>
@@ -3972,13 +3980,13 @@
         <v>10</v>
       </c>
       <c r="F57" t="s" s="3">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G57" t="s" s="3">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H57" t="s" s="3">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
@@ -3987,10 +3995,10 @@
     <row r="58" ht="13.65" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C58" t="s" s="3">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D58" s="7">
         <v>45781</v>
@@ -3999,7 +4007,7 @@
         <v>10</v>
       </c>
       <c r="F58" t="s" s="3">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G58" t="s" s="3">
         <v>147</v>
@@ -4008,20 +4016,20 @@
         <v>108</v>
       </c>
       <c r="I58" t="s" s="3">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J58" t="s" s="3">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K58" s="4"/>
     </row>
     <row r="59" ht="13.65" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C59" t="s" s="3">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D59" s="7">
         <v>45781</v>
@@ -4030,13 +4038,13 @@
         <v>10</v>
       </c>
       <c r="F59" t="s" s="3">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G59" t="s" s="3">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H59" t="s" s="3">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
@@ -4045,25 +4053,25 @@
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C60" t="s" s="3">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D60" t="s" s="6">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E60" t="s" s="6">
         <v>10</v>
       </c>
       <c r="F60" t="s" s="3">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G60" t="s" s="3">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H60" t="s" s="3">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
@@ -4074,10 +4082,10 @@
         <v>45724</v>
       </c>
       <c r="B61" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C61" t="s" s="3">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D61" s="9">
         <v>4</v>
@@ -4086,13 +4094,13 @@
         <v>10</v>
       </c>
       <c r="F61" t="s" s="3">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G61" t="s" s="3">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H61" t="s" s="3">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
@@ -4101,10 +4109,10 @@
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C62" t="s" s="3">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D62" s="7">
         <v>45781</v>
@@ -4113,13 +4121,13 @@
         <v>10</v>
       </c>
       <c r="F62" t="s" s="3">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G62" t="s" s="3">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="H62" t="s" s="3">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
@@ -4128,7 +4136,7 @@
     <row r="63" ht="13.65" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>247</v>
@@ -4155,7 +4163,7 @@
     <row r="64" ht="13.65" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C64" t="s" s="3">
         <v>251</v>
@@ -4182,7 +4190,7 @@
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C65" t="s" s="3">
         <v>255</v>
@@ -4209,7 +4217,7 @@
     <row r="66" ht="13.65" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" t="s" s="6">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C66" t="s" s="3">
         <v>259</v>
@@ -4313,10 +4321,10 @@
         <v>274</v>
       </c>
       <c r="I69" t="s" s="3">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J69" t="s" s="3">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K69" s="4"/>
     </row>
@@ -4476,7 +4484,7 @@
         <v>297</v>
       </c>
       <c r="H75" t="s" s="3">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
@@ -4488,7 +4496,7 @@
         <v>78</v>
       </c>
       <c r="C76" t="s" s="3">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D76" s="7">
         <v>45781</v>
@@ -4497,10 +4505,10 @@
         <v>10</v>
       </c>
       <c r="F76" t="s" s="3">
+        <v>299</v>
+      </c>
+      <c r="G76" t="s" s="3">
         <v>300</v>
-      </c>
-      <c r="G76" t="s" s="3">
-        <v>301</v>
       </c>
       <c r="H76" t="s" s="3">
         <v>112</v>
@@ -4515,7 +4523,7 @@
         <v>78</v>
       </c>
       <c r="C77" t="s" s="3">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D77" s="7">
         <v>45750</v>
@@ -4524,13 +4532,13 @@
         <v>10</v>
       </c>
       <c r="F77" t="s" s="3">
+        <v>302</v>
+      </c>
+      <c r="G77" t="s" s="3">
         <v>303</v>
       </c>
-      <c r="G77" t="s" s="3">
-        <v>304</v>
-      </c>
       <c r="H77" t="s" s="3">
-        <v>305</v>
+        <v>212</v>
       </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -4542,7 +4550,7 @@
         <v>78</v>
       </c>
       <c r="C78" t="s" s="3">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D78" s="7">
         <v>45781</v>
@@ -4551,13 +4559,13 @@
         <v>10</v>
       </c>
       <c r="F78" t="s" s="3">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G78" t="s" s="3">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="H78" t="s" s="3">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
@@ -4569,7 +4577,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="s" s="3">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D79" s="7">
         <v>45750</v>
@@ -4578,13 +4586,13 @@
         <v>10</v>
       </c>
       <c r="F79" t="s" s="3">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G79" t="s" s="3">
-        <v>311</v>
+        <v>151</v>
       </c>
       <c r="H79" t="s" s="3">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
@@ -4596,7 +4604,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s" s="3">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D80" s="7">
         <v>45781</v>
@@ -4605,13 +4613,13 @@
         <v>10</v>
       </c>
       <c r="F80" t="s" s="3">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G80" t="s" s="3">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H80" t="s" s="3">
-        <v>316</v>
+        <v>147</v>
       </c>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
@@ -4623,7 +4631,7 @@
         <v>78</v>
       </c>
       <c r="C81" t="s" s="3">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D81" s="9">
         <v>4</v>
@@ -4632,13 +4640,13 @@
         <v>10</v>
       </c>
       <c r="F81" t="s" s="3">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G81" t="s" s="3">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H81" t="s" s="3">
-        <v>273</v>
+        <v>315</v>
       </c>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
@@ -4650,7 +4658,7 @@
         <v>78</v>
       </c>
       <c r="C82" t="s" s="3">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D82" s="7">
         <v>45781</v>
@@ -4659,13 +4667,13 @@
         <v>10</v>
       </c>
       <c r="F82" t="s" s="3">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G82" t="s" s="3">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H82" t="s" s="3">
-        <v>323</v>
+        <v>174</v>
       </c>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
@@ -4677,7 +4685,7 @@
         <v>78</v>
       </c>
       <c r="C83" t="s" s="3">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D83" s="7">
         <v>45750</v>
@@ -4686,10 +4694,10 @@
         <v>10</v>
       </c>
       <c r="F83" t="s" s="3">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G83" t="s" s="3">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H83" t="s" s="3">
         <v>39</v>
@@ -4704,7 +4712,7 @@
         <v>78</v>
       </c>
       <c r="C84" t="s" s="3">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D84" s="7">
         <v>45781</v>
@@ -4713,13 +4721,13 @@
         <v>10</v>
       </c>
       <c r="F84" t="s" s="3">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G84" t="s" s="3">
-        <v>189</v>
+        <v>324</v>
       </c>
       <c r="H84" t="s" s="3">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -4731,7 +4739,7 @@
         <v>78</v>
       </c>
       <c r="C85" t="s" s="3">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D85" s="7">
         <v>45781</v>
@@ -4740,25 +4748,27 @@
         <v>10</v>
       </c>
       <c r="F85" t="s" s="3">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G85" t="s" s="3">
         <v>182</v>
       </c>
       <c r="H85" t="s" s="3">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
     </row>
     <row r="86" ht="13.65" customHeight="1">
-      <c r="A86" s="4"/>
+      <c r="A86" t="s" s="3">
+        <v>329</v>
+      </c>
       <c r="B86" t="s" s="6">
         <v>279</v>
       </c>
       <c r="C86" t="s" s="3">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D86" s="9">
         <v>5</v>
@@ -4767,15 +4777,17 @@
         <v>10</v>
       </c>
       <c r="F86" t="s" s="3">
+        <v>331</v>
+      </c>
+      <c r="G86" t="s" s="3">
+        <v>332</v>
+      </c>
+      <c r="H86" t="s" s="3">
         <v>333</v>
       </c>
-      <c r="G86" t="s" s="3">
+      <c r="I86" t="s" s="3">
         <v>334</v>
       </c>
-      <c r="H86" t="s" s="3">
-        <v>335</v>
-      </c>
-      <c r="I86" s="4"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
     </row>
@@ -4785,7 +4797,7 @@
         <v>279</v>
       </c>
       <c r="C87" t="s" s="3">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D87" s="7">
         <v>45781</v>
@@ -4794,10 +4806,10 @@
         <v>10</v>
       </c>
       <c r="F87" t="s" s="3">
+        <v>336</v>
+      </c>
+      <c r="G87" t="s" s="3">
         <v>337</v>
-      </c>
-      <c r="G87" t="s" s="3">
-        <v>63</v>
       </c>
       <c r="H87" t="s" s="3">
         <v>338</v>
@@ -4826,10 +4838,10 @@
         <v>340</v>
       </c>
       <c r="G88" t="s" s="3">
-        <v>181</v>
+        <v>341</v>
       </c>
       <c r="H88" t="s" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
@@ -4841,7 +4853,7 @@
         <v>78</v>
       </c>
       <c r="C89" t="s" s="3">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D89" s="7">
         <v>45781</v>
@@ -4850,13 +4862,13 @@
         <v>10</v>
       </c>
       <c r="F89" t="s" s="3">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G89" t="s" s="3">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H89" t="s" s="3">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
@@ -4868,7 +4880,7 @@
         <v>78</v>
       </c>
       <c r="C90" t="s" s="3">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D90" s="7">
         <v>45781</v>
@@ -4877,13 +4889,13 @@
         <v>10</v>
       </c>
       <c r="F90" t="s" s="3">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G90" t="s" s="3">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H90" t="s" s="3">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -4895,7 +4907,7 @@
         <v>78</v>
       </c>
       <c r="C91" t="s" s="3">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D91" s="7">
         <v>45750</v>
@@ -4904,13 +4916,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="s" s="3">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G91" t="s" s="3">
         <v>55</v>
       </c>
       <c r="H91" t="s" s="3">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
@@ -4922,7 +4934,7 @@
         <v>8</v>
       </c>
       <c r="C92" t="s" s="3">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D92" s="7">
         <v>45750</v>
@@ -4931,13 +4943,13 @@
         <v>10</v>
       </c>
       <c r="F92" t="s" s="3">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G92" t="s" s="3">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H92" t="s" s="3">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
@@ -4949,7 +4961,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="s" s="3">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D93" s="9">
         <v>4</v>
@@ -4958,13 +4970,13 @@
         <v>10</v>
       </c>
       <c r="F93" t="s" s="3">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G93" t="s" s="3">
         <v>174</v>
       </c>
       <c r="H93" t="s" s="3">
-        <v>355</v>
+        <v>204</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
@@ -4978,7 +4990,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s" s="3">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D94" s="9">
         <v>5</v>
@@ -4987,7 +4999,7 @@
         <v>10</v>
       </c>
       <c r="F94" t="s" s="3">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G94" t="s" s="3">
         <v>62</v>
@@ -5005,7 +5017,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s" s="3">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D95" s="9">
         <v>5</v>
@@ -5014,13 +5026,13 @@
         <v>10</v>
       </c>
       <c r="F95" t="s" s="3">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G95" t="s" s="3">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="H95" t="s" s="3">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
@@ -5032,7 +5044,7 @@
         <v>81</v>
       </c>
       <c r="C96" t="s" s="3">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D96" s="9">
         <v>5</v>
@@ -5041,13 +5053,13 @@
         <v>10</v>
       </c>
       <c r="F96" t="s" s="3">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G96" t="s" s="3">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H96" t="s" s="3">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
@@ -5059,7 +5071,7 @@
         <v>81</v>
       </c>
       <c r="C97" t="s" s="3">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D97" s="9">
         <v>5</v>
@@ -5068,16 +5080,16 @@
         <v>10</v>
       </c>
       <c r="F97" t="s" s="3">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G97" t="s" s="3">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H97" t="s" s="3">
         <v>174</v>
       </c>
       <c r="I97" t="s" s="3">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
@@ -5088,7 +5100,7 @@
         <v>81</v>
       </c>
       <c r="C98" t="s" s="3">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D98" s="9">
         <v>5</v>
@@ -5097,13 +5109,13 @@
         <v>10</v>
       </c>
       <c r="F98" t="s" s="3">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G98" t="s" s="3">
         <v>38</v>
       </c>
       <c r="H98" t="s" s="3">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
@@ -5115,7 +5127,7 @@
         <v>69</v>
       </c>
       <c r="C99" t="s" s="3">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D99" s="9">
         <v>5</v>
@@ -5124,13 +5136,13 @@
         <v>10</v>
       </c>
       <c r="F99" t="s" s="3">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G99" t="s" s="3">
-        <v>133</v>
+        <v>373</v>
       </c>
       <c r="H99" t="s" s="3">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
@@ -5142,7 +5154,7 @@
         <v>69</v>
       </c>
       <c r="C100" t="s" s="3">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D100" s="9">
         <v>5</v>
@@ -5151,13 +5163,13 @@
         <v>10</v>
       </c>
       <c r="F100" t="s" s="3">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G100" t="s" s="3">
-        <v>173</v>
+        <v>377</v>
       </c>
       <c r="H100" t="s" s="3">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
@@ -5169,7 +5181,7 @@
         <v>69</v>
       </c>
       <c r="C101" t="s" s="3">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D101" s="9">
         <v>5</v>
@@ -5178,13 +5190,13 @@
         <v>10</v>
       </c>
       <c r="F101" t="s" s="3">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G101" t="s" s="3">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H101" t="s" s="3">
-        <v>331</v>
+        <v>115</v>
       </c>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
@@ -5196,7 +5208,7 @@
         <v>69</v>
       </c>
       <c r="C102" t="s" s="3">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D102" s="9">
         <v>6</v>
@@ -5205,13 +5217,13 @@
         <v>10</v>
       </c>
       <c r="F102" t="s" s="3">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G102" t="s" s="3">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="H102" t="s" s="3">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
@@ -5223,7 +5235,7 @@
         <v>69</v>
       </c>
       <c r="C103" t="s" s="3">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D103" s="7">
         <v>45813</v>
@@ -5232,13 +5244,13 @@
         <v>10</v>
       </c>
       <c r="F103" t="s" s="3">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G103" t="s" s="3">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="H103" t="s" s="3">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
